--- a/demo_output/figure_00_Danmark vs. Sverige — BNP-vækst (%).xlsx
+++ b/demo_output/figure_00_Danmark vs. Sverige — BNP-vækst (%).xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grafik" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Danmark — BNP-vækst (%)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sverige — BNP-vækst (%)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Danmark — BNP-vækst" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sverige — BNP-vækst" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Danmark — BNP-vækst (%)</t>
+          <t>Danmark — BNP-vækst</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Sverige — BNP-vækst (%)</t>
+          <t>Sverige — BNP-vækst</t>
         </is>
       </c>
     </row>

--- a/demo_output/figure_00_Danmark vs. Sverige — BNP-vækst (%).xlsx
+++ b/demo_output/figure_00_Danmark vs. Sverige — BNP-vækst (%).xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grafik" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Danmark — BNP-vækst" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sverige — BNP-vækst" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sverige — BNP-vækst" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Danmark — BNP-vækst" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,208 +483,58 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Danmark — BNP-vækst</t>
+          <t>Sverige — BNP-vækst</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2005-01-01</t>
+          <t>2020-01-01</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>2.35960882992528</v>
+        <v>-1.93379704032216</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2006-01-01</t>
+          <t>2021-01-01</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>3.81648769908172</v>
+        <v>5.2258643028773</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
+          <t>2022-01-01</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.987173815945127</v>
+        <v>1.25543620445816</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2023-01-01</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>-0.417178439991005</v>
+        <v>-0.204061304891439</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2024-01-01</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>-4.97447905669058</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>2010-01-01</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>1.58289703108802</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>2011-01-01</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>1.3108037609606</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>2012-01-01</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>-0.00543230161670749</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>2013-01-01</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>1.39267343161971</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>1.27799983192831</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>2015-01-01</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>2.10441456445301</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>2016-01-01</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>3.07304549209093</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>2017-01-01</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>3.05647723922718</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>2018-01-01</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>1.8600074900921</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>2019-01-01</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>1.71140093932736</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>2020-01-01</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>-1.78010601831291</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>2021-01-01</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>6.50025445756295</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>0.443832614908331</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>2023-01-01</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>0.604587766175584</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>2024-01-01</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>3.47783593140312</v>
+        <v>0.820071806703865</v>
       </c>
     </row>
   </sheetData>
@@ -698,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -709,208 +559,58 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Sverige — BNP-vækst</t>
+          <t>Danmark — BNP-vækst</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2005-01-01</t>
+          <t>2020-01-01</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>2.79313782840156</v>
+        <v>-1.78010601831291</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2006-01-01</t>
+          <t>2021-01-01</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>4.67607488877992</v>
+        <v>6.50025445756295</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
+          <t>2022-01-01</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3.22486814096095</v>
+        <v>0.443832614908331</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2023-01-01</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>-0.923113250067971</v>
+        <v>0.604587766175584</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2024-01-01</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>-4.25561384207619</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>2010-01-01</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>5.75076477579255</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>2011-01-01</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>3.16388567406926</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>2012-01-01</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>-0.414397702454409</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>2013-01-01</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>1.13766671801426</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>2.29577238758284</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>2015-01-01</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>4.38824673608589</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>2016-01-01</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>2.13117914731151</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>2017-01-01</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>1.88282184966646</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>2018-01-01</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>1.7702553546772</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>2019-01-01</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>2.60823012869524</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>2020-01-01</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>-1.93379704032216</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>2021-01-01</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>5.2258643028773</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>1.25543620445816</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>2023-01-01</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>-0.204061304891439</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>2024-01-01</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>0.820071806703865</v>
+        <v>3.47783593140312</v>
       </c>
     </row>
   </sheetData>
